--- a/output/variables.xlsx
+++ b/output/variables.xlsx
@@ -1,101 +1,184 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
-  <workbookPr/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/0ebd9e082fb83b78/Sociologia/CONCLAT/employer associations and power/Employer-associations-and-power-1/output/"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="2" documentId="11_9CFAB22CF0F1A7FB56E72ABF073E1B9392599B80" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{FD406E4B-15DC-4B6F-A524-7F10FB26EEFB}"/>
+  <workbookPr date1904="false"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="13125" windowHeight="6105" firstSheet="0" activeTab="0"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet 1" sheetId="1" r:id="rId1"/>
+    <sheet name="Sheet 1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="30" uniqueCount="23">
-  <si>
-    <t>Variable</t>
-  </si>
-  <si>
-    <t>Tipo</t>
-  </si>
-  <si>
-    <t>Detalle</t>
-  </si>
-  <si>
-    <t>factor</t>
-  </si>
-  <si>
-    <t>numeric</t>
-  </si>
-  <si>
-    <t>economic_industry</t>
-  </si>
-  <si>
-    <t>Agricultura, ganadería, silvicultura y pesca; Minería; Industria manufacturera; Suministro de electricidad, gas y agua; Gestión de desechos; Construcción; Comercio; Transporte, almacenamiento, información y comunicaciones; Alojamiento y servicio de comidas; Actividades financieras y de seguros; Actividades inmobiliarias; Actividades profesionales y técnicas; Servicios administrativos y de apoyo; Enseñanza; Salud y asistencia social; Actividades artísticas y recreativas; Otros servicios</t>
-  </si>
-  <si>
-    <t>company_size</t>
-  </si>
-  <si>
-    <t>1; 2; 3</t>
-  </si>
-  <si>
-    <t>temporary_workers</t>
-  </si>
-  <si>
-    <t>Min: 0 | Max: 100 | Media: 20.36</t>
-  </si>
-  <si>
-    <t>part_time_workers</t>
-  </si>
-  <si>
-    <t>Min: 0 | Max: 100 | Media: 4.28</t>
-  </si>
-  <si>
-    <t>managers_workforce</t>
-  </si>
-  <si>
-    <t>Min: 0 | Max: 100 | Media: 17.94</t>
-  </si>
-  <si>
-    <t>female_employees</t>
-  </si>
-  <si>
-    <t>Min: 0 | Max: 100 | Media: 39.89</t>
-  </si>
-  <si>
-    <t>exports_products</t>
-  </si>
-  <si>
-    <t>Min: 0 | Max: 1 | Media: 0.07</t>
-  </si>
-  <si>
-    <t>subcontracts_workers</t>
-  </si>
-  <si>
-    <t>Min: 0 | Max: 1 | Media: 0.42</t>
-  </si>
-  <si>
-    <t>subcontractor_company</t>
-  </si>
-  <si>
-    <t>Min: 0 | Max: 1 | Media: 0.14</t>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="53" uniqueCount="53">
+  <si>
+    <t xml:space="preserve">Variable</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tipo</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Detalle</t>
+  </si>
+  <si>
+    <t xml:space="preserve">id</t>
+  </si>
+  <si>
+    <t xml:space="preserve">factor</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1234949; 1234950; 1236503; 1238262; 1238581; 1239057; 1239850; 1240752; 1243075; 1243253; 1243267; 1243440; 1250319; 1251167; 1251358; 1251458; 1251814; 1252089; 1252809; 1255267; ... (; 4496;  categorías en total)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">fe</t>
+  </si>
+  <si>
+    <t xml:space="preserve">numeric</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Min: 1 | Max: 3671.02426651027 | Media: 29.39</t>
+  </si>
+  <si>
+    <t xml:space="preserve">estrato</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Min: 1 | Max: 775 | Media: 385.5</t>
+  </si>
+  <si>
+    <t xml:space="preserve">employer_association</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Min: 0 | Max: 1 | Media: 0.25</t>
+  </si>
+  <si>
+    <t xml:space="preserve">union</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Min: 0 | Max: 1 | Media: 0.2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">union_density</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Min: 0 | Max: 100 | Media: 10.27</t>
+  </si>
+  <si>
+    <t xml:space="preserve">union_density_cat</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0; 1; 2; 3; 4; 5; 6; 7</t>
+  </si>
+  <si>
+    <t xml:space="preserve">fragmentation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0; 1; 2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">collective_bargaining_coverage</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Min: 0 | Max: 12 | Media: 4.42</t>
+  </si>
+  <si>
+    <t xml:space="preserve">confederation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Min: 0 | Max: 1 | Media: 0.38</t>
+  </si>
+  <si>
+    <t xml:space="preserve">legal_mobilization</t>
+  </si>
+  <si>
+    <t xml:space="preserve">integer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Min: 0 | Max: 1 | Media: 0.43</t>
+  </si>
+  <si>
+    <t xml:space="preserve">strikes</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Min: 0 | Max: 1 | Media: 0.05</t>
+  </si>
+  <si>
+    <t xml:space="preserve">economic_industry</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Agricultura, ganadería, silvicultura y pesca; Minería; Industria manufacturera; Suministro de electricidad, gas y agua; Gestión de desechos; Construcción; Comercio; Transporte, almacenamiento, información y comunicaciones; Alojamiento y servicio de comidas; Actividades financieras y de seguros; Actividades inmobiliarias; Actividades profesionales y técnicas; Servicios administrativos y de apoyo; Enseñanza; Salud y asistencia social; Actividades artísticas y recreativas; Otros servicios</t>
+  </si>
+  <si>
+    <t xml:space="preserve">company_size</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1; 2; 3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">temporary_workers</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Min: 0 | Max: 100 | Media: 20.36</t>
+  </si>
+  <si>
+    <t xml:space="preserve">part_time_workers</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Min: 0 | Max: 100 | Media: 4.28</t>
+  </si>
+  <si>
+    <t xml:space="preserve">managers_workforce</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Min: 0 | Max: 100 | Media: 17.94</t>
+  </si>
+  <si>
+    <t xml:space="preserve">female_employees</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Min: 0 | Max: 100 | Media: 39.89</t>
+  </si>
+  <si>
+    <t xml:space="preserve">exports_products</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Min: 0 | Max: 1 | Media: 0.07</t>
+  </si>
+  <si>
+    <t xml:space="preserve">subcontracts_workers</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Min: 0 | Max: 1 | Media: 0.42</t>
+  </si>
+  <si>
+    <t xml:space="preserve">subcontractor_company</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Min: 0 | Max: 1 | Media: 0.14</t>
+  </si>
+  <si>
+    <t xml:space="preserve">k3_3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">haven_labelled_spss</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Min: 3 | Max: 14192 | Media: 495.63</t>
+  </si>
+  <si>
+    <t xml:space="preserve">b1_3_7</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Min: 5 | Max: 18437 | Media: 266.18</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="1" x14ac:knownFonts="1">
+  <numFmts count="0"/>
+  <fonts count="1">
     <font>
       <sz val="11"/>
       <color rgb="FF000000"/>
@@ -131,15 +214,6 @@
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
-  <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
-      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
-    </ext>
-  </extLst>
 </styleSheet>
 </file>
 
@@ -421,11 +495,11 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:C10"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="15.0" baseColWidth="10"/>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="1">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -436,73 +510,73 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="2">
       <c r="A2" t="s">
+        <v>3</v>
+      </c>
+      <c r="B2" t="s">
+        <v>4</v>
+      </c>
+      <c r="C2" t="s">
         <v>5</v>
       </c>
-      <c r="B2" t="s">
-        <v>3</v>
-      </c>
-      <c r="C2" t="s">
+    </row>
+    <row r="3">
+      <c r="A3" t="s">
         <v>6</v>
       </c>
-    </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.45">
-      <c r="A3" t="s">
-        <v>7</v>
-      </c>
       <c r="B3" t="s">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="C3" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="4">
       <c r="A4" t="s">
         <v>9</v>
       </c>
       <c r="B4" t="s">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="C4" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="5">
       <c r="A5" t="s">
         <v>11</v>
       </c>
       <c r="B5" t="s">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="C5" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="6">
       <c r="A6" t="s">
         <v>13</v>
       </c>
       <c r="B6" t="s">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="C6" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="7">
       <c r="A7" t="s">
         <v>15</v>
       </c>
       <c r="B7" t="s">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="C7" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="8">
       <c r="A8" t="s">
         <v>17</v>
       </c>
@@ -513,7 +587,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="9">
       <c r="A9" t="s">
         <v>19</v>
       </c>
@@ -524,19 +598,173 @@
         <v>20</v>
       </c>
     </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="10">
       <c r="A10" t="s">
         <v>21</v>
       </c>
       <c r="B10" t="s">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="C10" t="s">
         <v>22</v>
       </c>
     </row>
+    <row r="11">
+      <c r="A11" t="s">
+        <v>23</v>
+      </c>
+      <c r="B11" t="s">
+        <v>7</v>
+      </c>
+      <c r="C11" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="s">
+        <v>25</v>
+      </c>
+      <c r="B12" t="s">
+        <v>26</v>
+      </c>
+      <c r="C12" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="s">
+        <v>28</v>
+      </c>
+      <c r="B13" t="s">
+        <v>26</v>
+      </c>
+      <c r="C13" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="s">
+        <v>30</v>
+      </c>
+      <c r="B14" t="s">
+        <v>4</v>
+      </c>
+      <c r="C14" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="s">
+        <v>32</v>
+      </c>
+      <c r="B15" t="s">
+        <v>4</v>
+      </c>
+      <c r="C15" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="s">
+        <v>34</v>
+      </c>
+      <c r="B16" t="s">
+        <v>7</v>
+      </c>
+      <c r="C16" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="s">
+        <v>36</v>
+      </c>
+      <c r="B17" t="s">
+        <v>7</v>
+      </c>
+      <c r="C17" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="s">
+        <v>38</v>
+      </c>
+      <c r="B18" t="s">
+        <v>7</v>
+      </c>
+      <c r="C18" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="s">
+        <v>40</v>
+      </c>
+      <c r="B19" t="s">
+        <v>7</v>
+      </c>
+      <c r="C19" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="s">
+        <v>42</v>
+      </c>
+      <c r="B20" t="s">
+        <v>7</v>
+      </c>
+      <c r="C20" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="s">
+        <v>44</v>
+      </c>
+      <c r="B21" t="s">
+        <v>7</v>
+      </c>
+      <c r="C21" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="s">
+        <v>46</v>
+      </c>
+      <c r="B22" t="s">
+        <v>7</v>
+      </c>
+      <c r="C22" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="s">
+        <v>48</v>
+      </c>
+      <c r="B23" t="s">
+        <v>49</v>
+      </c>
+      <c r="C23" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="s">
+        <v>51</v>
+      </c>
+      <c r="B24" t="s">
+        <v>49</v>
+      </c>
+      <c r="C24" t="s">
+        <v>52</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>
 </worksheet>
 </file>